--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="382">
   <si>
     <t>#</t>
   </si>
@@ -334,10 +334,34 @@
     <t>低概率刷新低于当前地图的区域boss</t>
   </si>
   <si>
-    <t>龙胆枪</t>
-  </si>
-  <si>
-    <t>诸葛连弩</t>
+    <t>冰霜之甲</t>
+  </si>
+  <si>
+    <t>1001,1002,95</t>
+  </si>
+  <si>
+    <t>30,20,4</t>
+  </si>
+  <si>
+    <t>40000030,40000033,40000036</t>
+  </si>
+  <si>
+    <t>40,40,40</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_2</t>
+  </si>
+  <si>
+    <t>解锁神器冰霜之甲</t>
+  </si>
+  <si>
+    <t>冰霜之戒</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_5</t>
+  </si>
+  <si>
+    <t>解锁神器冰霜之戒</t>
   </si>
   <si>
     <t>粗铁刀</t>
@@ -1169,7 +1193,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1193,12 +1217,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF333333"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF05073B"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1671,13 +1689,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1686,122 +1707,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1824,7 +1842,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2313,16 +2330,16 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="10" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="1">
@@ -2354,16 +2371,16 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="10" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="1">
@@ -2395,16 +2412,16 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L8" s="1">
@@ -2436,16 +2453,16 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L9" s="1">
@@ -2477,16 +2494,16 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="10" t="s">
         <v>45</v>
       </c>
       <c r="L10" s="1">
@@ -2518,16 +2535,16 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="10" t="s">
         <v>45</v>
       </c>
       <c r="L11" s="1">
@@ -2559,16 +2576,16 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="10" t="s">
         <v>45</v>
       </c>
       <c r="L12" s="1">
@@ -2600,16 +2617,16 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="10" t="s">
         <v>45</v>
       </c>
       <c r="L13" s="1">
@@ -2642,28 +2659,28 @@
       <c r="N16" s="1"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D18" s="7"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D19" s="5"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D20" s="9"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D21" s="5"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D22" s="7"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D23" s="7"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="1">
         <v>101</v>
       </c>
@@ -2679,16 +2696,16 @@
       <c r="G24" s="1">
         <v>0</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="10" t="s">
         <v>67</v>
       </c>
       <c r="L24" s="1">
@@ -2704,7 +2721,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="1">
         <v>102</v>
       </c>
@@ -2720,16 +2737,16 @@
       <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="10" t="s">
         <v>67</v>
       </c>
       <c r="L25" s="1">
@@ -2745,7 +2762,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="1">
         <v>103</v>
       </c>
@@ -2761,16 +2778,16 @@
       <c r="G26" s="1">
         <v>0</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="10" t="s">
         <v>67</v>
       </c>
       <c r="L26" s="1">
@@ -2783,7 +2800,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="1">
         <v>104</v>
       </c>
@@ -2799,16 +2816,16 @@
       <c r="G27" s="1">
         <v>0</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="10" t="s">
         <v>85</v>
       </c>
       <c r="L27" s="1">
@@ -2821,7 +2838,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="1">
         <v>105</v>
       </c>
@@ -2837,16 +2854,16 @@
       <c r="G28" s="1">
         <v>0</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K28" s="10" t="s">
         <v>85</v>
       </c>
       <c r="L28" s="1">
@@ -2862,7 +2879,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="1">
         <v>106</v>
       </c>
@@ -2878,16 +2895,16 @@
       <c r="G29" s="1">
         <v>0</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J29" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="K29" s="10" t="s">
         <v>67</v>
       </c>
       <c r="L29" s="1">
@@ -2903,26 +2920,80 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="10" t="s">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C30" s="1">
+        <v>107</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="10" t="s">
         <v>100</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L30" s="1">
+        <v>7</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C31" s="1">
+        <v>108</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L31" s="1">
+        <v>7</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="4:15">
@@ -3105,7 +3176,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3116,29 +3187,29 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="H6" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>104</v>
+      <c r="K6" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3146,7 +3217,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3157,29 +3228,29 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="H7" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>110</v>
+      <c r="K7" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3187,7 +3258,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3198,29 +3269,29 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="H8" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>113</v>
+      <c r="K8" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3228,7 +3299,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -3239,29 +3310,29 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="H9" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>116</v>
+      <c r="K9" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3275,7 +3346,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3286,17 +3357,17 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>121</v>
+      <c r="H10" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3305,7 +3376,7 @@
         <v>23</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3319,7 +3390,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3330,17 +3401,17 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>121</v>
+      <c r="H11" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3349,7 +3420,7 @@
         <v>23</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3363,7 +3434,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3374,17 +3445,17 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>131</v>
+      <c r="H12" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3393,7 +3464,7 @@
         <v>23</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3407,7 +3478,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3418,17 +3489,17 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>131</v>
+      <c r="H13" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3437,7 +3508,7 @@
         <v>23</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3451,7 +3522,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3462,17 +3533,17 @@
       <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="J14" s="11" t="s">
+      <c r="H14" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>131</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3481,7 +3552,7 @@
         <v>23</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
@@ -3494,7 +3565,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="N17" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3505,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3514,7 +3585,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3525,26 +3596,26 @@
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="J20" s="11" t="s">
+      <c r="H20" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K20" s="11" t="s">
-        <v>116</v>
+      <c r="K20" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3552,7 +3623,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3563,26 +3634,26 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J21" s="11" t="s">
+      <c r="H21" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="11" t="s">
-        <v>116</v>
+      <c r="K21" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3590,7 +3661,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3601,26 +3672,26 @@
       <c r="G22" s="1">
         <v>0</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="J22" s="11" t="s">
+      <c r="H22" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K22" s="11" t="s">
-        <v>116</v>
+      <c r="K22" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3628,7 +3699,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3639,26 +3710,26 @@
       <c r="G23" s="1">
         <v>0</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="J23" s="11" t="s">
+      <c r="H23" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="J23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K23" s="11" t="s">
-        <v>116</v>
+      <c r="K23" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3666,7 +3737,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3677,26 +3748,26 @@
       <c r="G24" s="1">
         <v>0</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>116</v>
+      <c r="H24" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3704,7 +3775,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3715,26 +3786,26 @@
       <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>116</v>
+      <c r="H25" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3742,7 +3813,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3753,26 +3824,26 @@
       <c r="G26" s="1">
         <v>0</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>116</v>
+      <c r="H26" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3788,7 +3859,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3799,23 +3870,23 @@
       <c r="G29" s="1">
         <v>10011</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>178</v>
+      <c r="H29" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3829,7 +3900,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3840,23 +3911,23 @@
       <c r="G30" s="1">
         <v>10021</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>178</v>
+      <c r="H30" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3870,7 +3941,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3881,23 +3952,23 @@
       <c r="G31" s="1">
         <v>10031</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>178</v>
+      <c r="H31" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3911,7 +3982,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3922,23 +3993,23 @@
       <c r="G32" s="1">
         <v>10041</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>188</v>
+      <c r="H32" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3952,7 +4023,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3963,23 +4034,23 @@
       <c r="G33" s="1">
         <v>10051</v>
       </c>
-      <c r="H33" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>188</v>
+      <c r="H33" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3993,7 +4064,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -4004,23 +4075,23 @@
       <c r="G34" s="1">
         <v>10061</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>188</v>
+      <c r="H34" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -4034,7 +4105,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4045,23 +4116,23 @@
       <c r="G35" s="1">
         <v>10071</v>
       </c>
-      <c r="H35" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>195</v>
+      <c r="H35" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="S35" s="6"/>
     </row>
@@ -4087,7 +4158,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4098,23 +4169,23 @@
       <c r="G37" s="1">
         <v>10012</v>
       </c>
-      <c r="H37" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>195</v>
+      <c r="H37" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="S37" s="6"/>
     </row>
@@ -4129,7 +4200,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4140,23 +4211,23 @@
       <c r="G38" s="1">
         <v>10022</v>
       </c>
-      <c r="H38" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="K38" s="11" t="s">
-        <v>195</v>
+      <c r="H38" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="S38" s="6"/>
     </row>
@@ -4171,7 +4242,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4182,23 +4253,23 @@
       <c r="G39" s="1">
         <v>10032</v>
       </c>
-      <c r="H39" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I39" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>177</v>
+      <c r="H39" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="1"/>
@@ -4215,7 +4286,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4226,23 +4297,23 @@
       <c r="G40" s="1">
         <v>10042</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>177</v>
+      <c r="H40" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="1"/>
@@ -4259,7 +4330,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4270,23 +4341,23 @@
       <c r="G41" s="1">
         <v>10052</v>
       </c>
-      <c r="H41" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K41" s="11" t="s">
-        <v>188</v>
+      <c r="H41" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="P41" s="6"/>
       <c r="S41" s="6"/>
@@ -4302,7 +4373,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4313,23 +4384,23 @@
       <c r="G42" s="1">
         <v>10072</v>
       </c>
-      <c r="H42" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I42" s="11" t="s">
+      <c r="H42" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J42" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J42" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K42" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="1"/>
@@ -4358,7 +4429,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4369,23 +4440,23 @@
       <c r="G44" s="1">
         <v>10023</v>
       </c>
-      <c r="H44" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>177</v>
+      <c r="H44" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="1"/>
@@ -4402,7 +4473,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4413,23 +4484,23 @@
       <c r="G45" s="1">
         <v>10073</v>
       </c>
-      <c r="H45" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>177</v>
+      <c r="H45" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="1"/>
@@ -4458,7 +4529,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4469,23 +4540,23 @@
       <c r="G47" s="1">
         <v>10024</v>
       </c>
-      <c r="H47" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I47" s="11" t="s">
+      <c r="H47" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J47" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J47" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K47" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4503,7 +4574,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4514,24 +4585,24 @@
       <c r="G48" s="1">
         <v>10034</v>
       </c>
-      <c r="H48" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I48" s="11" t="s">
+      <c r="H48" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J48" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J48" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="6"/>
@@ -4585,7 +4656,7 @@
         <v>1201</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -4596,26 +4667,26 @@
       <c r="G50" s="1">
         <v>0</v>
       </c>
-      <c r="H50" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="K50" s="11" t="s">
+      <c r="H50" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="K50" s="10" t="s">
         <v>85</v>
       </c>
       <c r="L50" s="1">
         <v>7</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:20 16374:16384">
@@ -5005,7 +5076,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -5016,23 +5087,23 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="H6" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>104</v>
+      <c r="K6" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -5056,7 +5127,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -5067,23 +5138,23 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="H7" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>110</v>
+      <c r="K7" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -5107,7 +5178,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -5118,23 +5189,23 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="H8" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>113</v>
+      <c r="K8" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -5158,7 +5229,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5169,23 +5240,23 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="H9" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>116</v>
+      <c r="K9" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -5213,7 +5284,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5224,17 +5295,17 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>121</v>
+      <c r="H10" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -5266,7 +5337,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5277,17 +5348,17 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>121</v>
+      <c r="H11" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5319,7 +5390,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5330,17 +5401,17 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>131</v>
+      <c r="H12" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5372,7 +5443,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5383,17 +5454,17 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>131</v>
+      <c r="H13" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5425,7 +5496,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5436,17 +5507,17 @@
       <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="J14" s="11" t="s">
+      <c r="H14" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>131</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5498,7 +5569,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5509,26 +5580,26 @@
       <c r="G16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="J16" s="11" t="s">
+      <c r="H16" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="11" t="s">
-        <v>116</v>
+      <c r="K16" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5536,7 +5607,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5547,26 +5618,26 @@
       <c r="G17" s="1">
         <v>0</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J17" s="11" t="s">
+      <c r="H17" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="11" t="s">
-        <v>116</v>
+      <c r="K17" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5574,7 +5645,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5585,26 +5656,26 @@
       <c r="G18" s="1">
         <v>0</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="J18" s="11" t="s">
+      <c r="H18" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="11" t="s">
-        <v>116</v>
+      <c r="K18" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5612,7 +5683,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5623,26 +5694,26 @@
       <c r="G19" s="1">
         <v>0</v>
       </c>
-      <c r="H19" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="J19" s="11" t="s">
+      <c r="H19" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K19" s="11" t="s">
-        <v>116</v>
+      <c r="K19" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5650,7 +5721,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5661,26 +5732,26 @@
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>116</v>
+      <c r="H20" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5688,7 +5759,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5699,26 +5770,26 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>116</v>
+      <c r="H21" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5726,7 +5797,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5737,26 +5808,26 @@
       <c r="G22" s="1">
         <v>0</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>116</v>
+      <c r="H22" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5774,7 +5845,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5785,24 +5856,24 @@
       <c r="G24" s="1">
         <v>20011</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>178</v>
+      <c r="H24" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="6" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="O24" s="2"/>
       <c r="XET24" s="1"/>
@@ -5828,7 +5899,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5839,24 +5910,24 @@
       <c r="G25" s="1">
         <v>20021</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>178</v>
+      <c r="H25" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="O25" s="1"/>
       <c r="XET25" s="1"/>
@@ -5882,7 +5953,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5893,24 +5964,24 @@
       <c r="G26" s="1">
         <v>20031</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>178</v>
+      <c r="H26" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="6" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="O26" s="1"/>
       <c r="XET26" s="1"/>
@@ -5936,7 +6007,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5947,24 +6018,24 @@
       <c r="G27" s="1">
         <v>20041</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>188</v>
+      <c r="H27" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="O27" s="1"/>
       <c r="XET27" s="1"/>
@@ -5990,7 +6061,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -6001,24 +6072,24 @@
       <c r="G28" s="1">
         <v>20051</v>
       </c>
-      <c r="H28" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>188</v>
+      <c r="H28" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="O28" s="1"/>
       <c r="XET28" s="1"/>
@@ -6044,7 +6115,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -6055,24 +6126,24 @@
       <c r="G29" s="1">
         <v>20061</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>188</v>
+      <c r="H29" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="O29" s="1"/>
       <c r="XET29" s="1"/>
@@ -6098,7 +6169,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -6109,24 +6180,24 @@
       <c r="G30" s="1">
         <v>20071</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>195</v>
+      <c r="H30" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="6" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="O30" s="1"/>
       <c r="XET30" s="1"/>
@@ -6184,7 +6255,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6195,24 +6266,24 @@
       <c r="G32" s="1">
         <v>20012</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>195</v>
+      <c r="H32" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="O32" s="1"/>
       <c r="XET32" s="1"/>
@@ -6238,7 +6309,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6249,24 +6320,24 @@
       <c r="G33" s="1">
         <v>20022</v>
       </c>
-      <c r="H33" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>195</v>
+      <c r="H33" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="O33" s="1"/>
       <c r="XET33" s="1"/>
@@ -6292,7 +6363,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6303,24 +6374,24 @@
       <c r="G34" s="1">
         <v>20032</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>177</v>
+      <c r="H34" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="6" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="O34" s="1"/>
       <c r="XET34" s="1"/>
@@ -6346,7 +6417,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6357,24 +6428,24 @@
       <c r="G35" s="1">
         <v>20052</v>
       </c>
-      <c r="H35" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>188</v>
+      <c r="H35" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="6" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O35" s="1"/>
       <c r="XET35" s="1"/>
@@ -6400,7 +6471,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6411,24 +6482,24 @@
       <c r="G36" s="1">
         <v>20072</v>
       </c>
-      <c r="H36" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>177</v>
+      <c r="H36" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="6" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="O36" s="1"/>
       <c r="XET36" s="1"/>
@@ -6486,7 +6557,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6497,24 +6568,24 @@
       <c r="G38" s="1">
         <v>20023</v>
       </c>
-      <c r="H38" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I38" s="11" t="s">
+      <c r="H38" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J38" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J38" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="O38" s="1"/>
       <c r="XET38" s="1"/>
@@ -6540,7 +6611,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6551,24 +6622,24 @@
       <c r="G39" s="1">
         <v>20043</v>
       </c>
-      <c r="H39" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I39" s="11" t="s">
+      <c r="H39" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J39" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J39" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="6" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="O39" s="1"/>
       <c r="XET39" s="1"/>
@@ -6594,7 +6665,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6605,23 +6676,23 @@
       <c r="G40" s="1">
         <v>20073</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>177</v>
+      <c r="H40" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -6655,7 +6726,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6666,23 +6737,23 @@
       <c r="G42" s="1">
         <v>20024</v>
       </c>
-      <c r="H42" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I42" s="11" t="s">
+      <c r="H42" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J42" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J42" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K42" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -6701,7 +6772,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6712,23 +6783,23 @@
       <c r="G43" s="1">
         <v>20034</v>
       </c>
-      <c r="H43" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I43" s="11" t="s">
+      <c r="H43" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J43" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J43" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K43" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -6748,7 +6819,7 @@
         <v>2201</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
@@ -6759,26 +6830,26 @@
       <c r="G45" s="1">
         <v>0</v>
       </c>
-      <c r="H45" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="K45" s="11" t="s">
+      <c r="H45" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="K45" s="10" t="s">
         <v>85</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:19 16374:16384">
@@ -7135,7 +7206,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -7146,23 +7217,23 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="H6" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>104</v>
+      <c r="K6" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -7173,7 +7244,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7184,23 +7255,23 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="H7" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>110</v>
+      <c r="K7" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -7211,7 +7282,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7222,23 +7293,23 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="H8" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>113</v>
+      <c r="K8" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -7250,7 +7321,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7261,23 +7332,23 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="H9" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>116</v>
+      <c r="K9" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -7295,7 +7366,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7306,17 +7377,17 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>121</v>
+      <c r="H10" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -7337,7 +7408,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7348,17 +7419,17 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>121</v>
+      <c r="H11" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -7379,7 +7450,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7390,17 +7461,17 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>131</v>
+      <c r="H12" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7421,7 +7492,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7432,17 +7503,17 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>131</v>
+      <c r="H13" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7463,7 +7534,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7474,17 +7545,17 @@
       <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="J14" s="11" t="s">
+      <c r="H14" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>131</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7502,7 +7573,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7513,26 +7584,26 @@
       <c r="G16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="J16" s="11" t="s">
+      <c r="H16" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="11" t="s">
-        <v>116</v>
+      <c r="K16" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7540,7 +7611,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7551,26 +7622,26 @@
       <c r="G17" s="1">
         <v>0</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J17" s="11" t="s">
+      <c r="H17" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="11" t="s">
-        <v>116</v>
+      <c r="K17" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7578,7 +7649,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7589,26 +7660,26 @@
       <c r="G18" s="1">
         <v>0</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="J18" s="11" t="s">
+      <c r="H18" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="11" t="s">
-        <v>116</v>
+      <c r="K18" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7616,7 +7687,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7627,26 +7698,26 @@
       <c r="G19" s="1">
         <v>0</v>
       </c>
-      <c r="H19" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="J19" s="11" t="s">
+      <c r="H19" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K19" s="11" t="s">
-        <v>116</v>
+      <c r="K19" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7654,7 +7725,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7665,26 +7736,26 @@
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>116</v>
+      <c r="H20" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7692,7 +7763,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7703,26 +7774,26 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>116</v>
+      <c r="H21" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7730,7 +7801,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7741,26 +7812,26 @@
       <c r="G22" s="1">
         <v>0</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>116</v>
+      <c r="H22" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7777,7 +7848,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7788,23 +7859,23 @@
       <c r="G24" s="1">
         <v>30011</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>178</v>
+      <c r="H24" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="O24" s="2"/>
     </row>
@@ -7819,7 +7890,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7830,23 +7901,23 @@
       <c r="G25" s="1">
         <v>30021</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>178</v>
+      <c r="H25" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="O25" s="2"/>
     </row>
@@ -7861,7 +7932,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7872,23 +7943,23 @@
       <c r="G26" s="1">
         <v>30031</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>178</v>
+      <c r="H26" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="O26" s="2"/>
     </row>
@@ -7903,7 +7974,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7914,23 +7985,23 @@
       <c r="G27" s="1">
         <v>30041</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>188</v>
+      <c r="H27" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="O27" s="2"/>
     </row>
@@ -7945,7 +8016,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7956,23 +8027,23 @@
       <c r="G28" s="1">
         <v>30051</v>
       </c>
-      <c r="H28" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>188</v>
+      <c r="H28" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="O28" s="2"/>
     </row>
@@ -7987,7 +8058,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7998,23 +8069,23 @@
       <c r="G29" s="1">
         <v>30061</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>188</v>
+      <c r="H29" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="O29" s="2"/>
     </row>
@@ -8029,7 +8100,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -8040,23 +8111,23 @@
       <c r="G30" s="1">
         <v>30071</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>195</v>
+      <c r="H30" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="O30" s="2"/>
     </row>
@@ -8080,7 +8151,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -8091,23 +8162,23 @@
       <c r="G32" s="1">
         <v>30012</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>195</v>
+      <c r="H32" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="O32" s="2"/>
     </row>
@@ -8122,7 +8193,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -8133,23 +8204,23 @@
       <c r="G33" s="1">
         <v>30022</v>
       </c>
-      <c r="H33" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>195</v>
+      <c r="H33" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="O33" s="2"/>
     </row>
@@ -8164,7 +8235,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8175,23 +8246,23 @@
       <c r="G34" s="1">
         <v>30032</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>177</v>
+      <c r="H34" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="O34" s="2"/>
     </row>
@@ -8206,7 +8277,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8217,23 +8288,23 @@
       <c r="G35" s="1">
         <v>30052</v>
       </c>
-      <c r="H35" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>120</v>
+      <c r="H35" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>128</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="O35" s="2"/>
     </row>
@@ -8257,7 +8328,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8268,23 +8339,23 @@
       <c r="G37" s="1">
         <v>30023</v>
       </c>
-      <c r="H37" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>139</v>
+      <c r="H37" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>147</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="O37" s="2"/>
     </row>
@@ -8299,7 +8370,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8310,23 +8381,23 @@
       <c r="G38" s="1">
         <v>30033</v>
       </c>
-      <c r="H38" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>177</v>
+      <c r="H38" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="O38" s="2"/>
     </row>
@@ -8341,7 +8412,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8352,23 +8423,23 @@
       <c r="G39" s="1">
         <v>30043</v>
       </c>
-      <c r="H39" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I39" s="11" t="s">
+      <c r="H39" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J39" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J39" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="O39" s="2"/>
     </row>
@@ -8383,7 +8454,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8394,23 +8465,23 @@
       <c r="G40" s="1">
         <v>30073</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>177</v>
+      <c r="H40" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="O40" s="2"/>
     </row>
@@ -8436,7 +8507,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8447,23 +8518,23 @@
       <c r="G42" s="1">
         <v>30024</v>
       </c>
-      <c r="H42" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I42" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>177</v>
+      <c r="H42" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="O42" s="2"/>
     </row>
@@ -8478,7 +8549,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8489,23 +8560,23 @@
       <c r="G43" s="1">
         <v>30034</v>
       </c>
-      <c r="H43" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I43" s="11" t="s">
+      <c r="H43" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J43" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="J43" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="K43" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -8539,7 +8610,7 @@
         <v>3201</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="E45" s="1">
         <v>3</v>
@@ -8550,26 +8621,26 @@
       <c r="G45" s="1">
         <v>0</v>
       </c>
-      <c r="H45" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="K45" s="11" t="s">
+      <c r="H45" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="K45" s="10" t="s">
         <v>85</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
